--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826029</v>
+        <v>128826137</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542756</v>
+        <v>542888</v>
       </c>
       <c r="R4" t="n">
-        <v>6369581</v>
+        <v>6369430</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826186</v>
+        <v>128826029</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542819</v>
+        <v>542756</v>
       </c>
       <c r="R5" t="n">
-        <v>6369555</v>
+        <v>6369581</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826137</v>
+        <v>128826186</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542888</v>
+        <v>542819</v>
       </c>
       <c r="R6" t="n">
-        <v>6369430</v>
+        <v>6369555</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826011</v>
+        <v>128826035</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,7 +1625,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542783</v>
+        <v>542725</v>
       </c>
       <c r="R10" t="n">
-        <v>6369619</v>
+        <v>6369561</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1697,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826035</v>
+        <v>128826011</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1731,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1735,11 +1739,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542725</v>
+        <v>542783</v>
       </c>
       <c r="R11" t="n">
-        <v>6369561</v>
+        <v>6369619</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826137</v>
+        <v>128826029</v>
       </c>
       <c r="B4" t="n">
         <v>98636</v>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542888</v>
+        <v>542756</v>
       </c>
       <c r="R4" t="n">
-        <v>6369430</v>
+        <v>6369581</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826029</v>
+        <v>128826186</v>
       </c>
       <c r="B5" t="n">
         <v>98636</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542756</v>
+        <v>542819</v>
       </c>
       <c r="R5" t="n">
-        <v>6369581</v>
+        <v>6369555</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826186</v>
+        <v>128826137</v>
       </c>
       <c r="B6" t="n">
         <v>98636</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542819</v>
+        <v>542888</v>
       </c>
       <c r="R6" t="n">
-        <v>6369555</v>
+        <v>6369430</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128825956</v>
+        <v>128826065</v>
       </c>
       <c r="B7" t="n">
         <v>98636</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542816</v>
+        <v>542858</v>
       </c>
       <c r="R7" t="n">
-        <v>6369644</v>
+        <v>6369516</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128826065</v>
+        <v>128825956</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542858</v>
+        <v>542816</v>
       </c>
       <c r="R8" t="n">
-        <v>6369516</v>
+        <v>6369644</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826035</v>
+        <v>128826011</v>
       </c>
       <c r="B10" t="n">
         <v>98636</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,11 +1625,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1638,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542725</v>
+        <v>542783</v>
       </c>
       <c r="R10" t="n">
-        <v>6369561</v>
+        <v>6369619</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1701,7 +1697,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826011</v>
+        <v>128826035</v>
       </c>
       <c r="B11" t="n">
         <v>98636</v>
@@ -1731,7 +1727,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1739,7 +1735,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542783</v>
+        <v>542725</v>
       </c>
       <c r="R11" t="n">
-        <v>6369619</v>
+        <v>6369561</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128826065</v>
+        <v>128825956</v>
       </c>
       <c r="B7" t="n">
         <v>98636</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542858</v>
+        <v>542816</v>
       </c>
       <c r="R7" t="n">
-        <v>6369516</v>
+        <v>6369644</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128825956</v>
+        <v>128826065</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542816</v>
+        <v>542858</v>
       </c>
       <c r="R8" t="n">
-        <v>6369644</v>
+        <v>6369516</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128826192</v>
+        <v>128826137</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542836</v>
+        <v>542888</v>
       </c>
       <c r="R3" t="n">
-        <v>6369482</v>
+        <v>6369430</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826186</v>
+        <v>128826192</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542819</v>
+        <v>542836</v>
       </c>
       <c r="R5" t="n">
-        <v>6369555</v>
+        <v>6369482</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826137</v>
+        <v>128826186</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542888</v>
+        <v>542819</v>
       </c>
       <c r="R6" t="n">
-        <v>6369430</v>
+        <v>6369555</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826095</v>
+        <v>128826206</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542776</v>
+        <v>542843</v>
       </c>
       <c r="R16" t="n">
-        <v>6369542</v>
+        <v>6369567</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826206</v>
+        <v>128826095</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542843</v>
+        <v>542776</v>
       </c>
       <c r="R17" t="n">
-        <v>6369567</v>
+        <v>6369542</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kenneth Rosén, Lena Carlsson</t>
+          <t>Lena Carlsson, Kenneth Rosén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Carlsson, Kenneth Rosén</t>
+          <t>Kenneth Rosén, Lena Carlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128826192</v>
+        <v>128826137</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542836</v>
+        <v>542888</v>
       </c>
       <c r="R3" t="n">
-        <v>6369482</v>
+        <v>6369430</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826029</v>
+        <v>128826192</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542756</v>
+        <v>542836</v>
       </c>
       <c r="R4" t="n">
-        <v>6369581</v>
+        <v>6369482</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826186</v>
+        <v>128826029</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542819</v>
+        <v>542756</v>
       </c>
       <c r="R5" t="n">
-        <v>6369555</v>
+        <v>6369581</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826137</v>
+        <v>128826186</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542888</v>
+        <v>542819</v>
       </c>
       <c r="R6" t="n">
-        <v>6369430</v>
+        <v>6369555</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826095</v>
+        <v>128826206</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542776</v>
+        <v>542843</v>
       </c>
       <c r="R16" t="n">
-        <v>6369542</v>
+        <v>6369567</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826206</v>
+        <v>128826095</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542843</v>
+        <v>542776</v>
       </c>
       <c r="R17" t="n">
-        <v>6369567</v>
+        <v>6369542</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128826137</v>
+        <v>128826192</v>
       </c>
       <c r="B3" t="n">
         <v>98669</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542888</v>
+        <v>542836</v>
       </c>
       <c r="R3" t="n">
-        <v>6369430</v>
+        <v>6369482</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128826192</v>
+        <v>128826029</v>
       </c>
       <c r="B4" t="n">
         <v>98669</v>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542836</v>
+        <v>542756</v>
       </c>
       <c r="R4" t="n">
-        <v>6369482</v>
+        <v>6369581</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128826029</v>
+        <v>128826186</v>
       </c>
       <c r="B5" t="n">
         <v>98669</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542756</v>
+        <v>542819</v>
       </c>
       <c r="R5" t="n">
-        <v>6369581</v>
+        <v>6369555</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128826186</v>
+        <v>128826137</v>
       </c>
       <c r="B6" t="n">
         <v>98669</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542819</v>
+        <v>542888</v>
       </c>
       <c r="R6" t="n">
-        <v>6369555</v>
+        <v>6369430</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128826206</v>
+        <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542843</v>
+        <v>542776</v>
       </c>
       <c r="R16" t="n">
-        <v>6369567</v>
+        <v>6369542</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128826095</v>
+        <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542776</v>
+        <v>542843</v>
       </c>
       <c r="R17" t="n">
-        <v>6369542</v>
+        <v>6369567</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826011</v>
+        <v>128826035</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,7 +1625,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1634,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542783</v>
+        <v>542725</v>
       </c>
       <c r="R10" t="n">
-        <v>6369619</v>
+        <v>6369561</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1697,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826035</v>
+        <v>128826011</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1731,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1735,11 +1739,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542725</v>
+        <v>542783</v>
       </c>
       <c r="R11" t="n">
-        <v>6369561</v>
+        <v>6369619</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 41605-2025 artfynd.xlsx
+++ b/artfynd/A 41605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826088</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128826192</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128826029</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>128826186</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>128826137</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>128825956</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128826065</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>128825991</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128826035</v>
+        <v>128826011</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,11 +1625,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1638,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542725</v>
+        <v>542783</v>
       </c>
       <c r="R10" t="n">
-        <v>6369561</v>
+        <v>6369619</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1701,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128826011</v>
+        <v>128826035</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1727,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1739,7 +1735,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542783</v>
+        <v>542725</v>
       </c>
       <c r="R11" t="n">
-        <v>6369619</v>
+        <v>6369561</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>128826051</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128826025</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128825949</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>128826105</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>128826095</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128826206</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
